--- a/data/trans_bre/P16-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 23,53</t>
+          <t>12,36; 23,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,09; 26,9</t>
+          <t>14,07; 27,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,53; 27,07</t>
+          <t>14,74; 27,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 23,17</t>
+          <t>3,42; 23,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,88; 131,45</t>
+          <t>54,74; 134,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,55; 109,67</t>
+          <t>45,81; 111,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,26; 142,06</t>
+          <t>55,82; 140,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 123,3</t>
+          <t>10,9; 118,52</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 28,44</t>
+          <t>18,3; 28,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 30,72</t>
+          <t>20,09; 30,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 20,24</t>
+          <t>8,75; 20,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 36,86</t>
+          <t>8,75; 38,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>82,35; 155,9</t>
+          <t>83,9; 158,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,79; 101,93</t>
+          <t>56,19; 101,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 68,41</t>
+          <t>24,53; 69,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,61; 122,25</t>
+          <t>22,6; 117,61</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,41; 22,96</t>
+          <t>13,04; 23,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,18; 28,89</t>
+          <t>17,77; 28,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 21,28</t>
+          <t>9,67; 20,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 16,78</t>
+          <t>5,24; 16,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,71; 93,97</t>
+          <t>42,71; 96,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,13; 85,41</t>
+          <t>45,02; 85,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,14; 63,77</t>
+          <t>24,53; 60,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,36; 47,29</t>
+          <t>12,24; 47,39</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,58; 23,1</t>
+          <t>10,1; 22,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 27,74</t>
+          <t>15,87; 27,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 15,04</t>
+          <t>3,74; 15,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 43,18</t>
+          <t>6,06; 44,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,7; 63,42</t>
+          <t>23,37; 61,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,49; 63,25</t>
+          <t>31,37; 61,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 31,8</t>
+          <t>6,6; 31,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 282,21</t>
+          <t>11,65; 230,46</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 8,17</t>
+          <t>-4,29; 8,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,5</t>
+          <t>2,39; 13,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,18</t>
+          <t>8,28; 20,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 8,99</t>
+          <t>-0,33; 9,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 11,73</t>
+          <t>-5,67; 11,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 19,09</t>
+          <t>3,0; 19,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 33,6</t>
+          <t>11,92; 32,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 13,33</t>
+          <t>-0,47; 13,35</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 17,25</t>
+          <t>5,62; 16,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 8,44</t>
+          <t>-1,25; 8,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 13,08</t>
+          <t>2,96; 12,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,52; 21,0</t>
+          <t>4,97; 21,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 23,16</t>
+          <t>6,89; 22,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 9,89</t>
+          <t>-1,38; 9,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,82; 16,38</t>
+          <t>3,36; 15,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 28,59</t>
+          <t>6,5; 29,02</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 9,58</t>
+          <t>-0,82; 9,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 6,97</t>
+          <t>0,17; 7,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,29</t>
+          <t>0,29; 8,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 9,15</t>
+          <t>1,65; 9,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 11,19</t>
+          <t>-0,82; 11,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,73</t>
+          <t>0,18; 8,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,47</t>
+          <t>0,32; 9,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 10,96</t>
+          <t>1,81; 11,79</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,7; 20,48</t>
+          <t>15,68; 20,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,37</t>
+          <t>17,36; 22,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,55</t>
+          <t>12,82; 17,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,2; 29,75</t>
+          <t>11,03; 29,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,43; 52,27</t>
+          <t>37,4; 52,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,9; 45,53</t>
+          <t>33,5; 45,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,97; 36,07</t>
+          <t>25,34; 35,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,34; 75,12</t>
+          <t>20,5; 75,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>13,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>53,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 23,35</t>
+          <t>12,46; 23,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 27,55</t>
+          <t>15,02; 27,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 27,1</t>
+          <t>13,95; 27,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 23,04</t>
+          <t>3,74; 23,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>54,74; 134,49</t>
+          <t>53,6; 132,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,81; 111,16</t>
+          <t>49,16; 117,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,82; 140,1</t>
+          <t>55,09; 148,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 118,52</t>
+          <t>11,67; 120,76</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>10,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,3; 28,35</t>
+          <t>18,01; 28,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,09; 30,66</t>
+          <t>20,16; 31,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,38</t>
+          <t>9,19; 20,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 38,17</t>
+          <t>3,17; 18,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,9; 158,26</t>
+          <t>81,97; 156,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,19; 101,52</t>
+          <t>57,28; 105,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,53; 69,1</t>
+          <t>26,03; 69,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,6; 117,61</t>
+          <t>8,44; 65,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,09</t>
+          <t>12,33</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,04; 23,53</t>
+          <t>12,83; 22,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,77; 28,9</t>
+          <t>18,49; 29,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 20,24</t>
+          <t>9,62; 20,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,24; 16,65</t>
+          <t>7,48; 18,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>42,71; 96,43</t>
+          <t>42,51; 93,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,02; 85,57</t>
+          <t>46,73; 84,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,53; 60,14</t>
+          <t>23,81; 58,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 47,39</t>
+          <t>18,12; 52,4</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,08</t>
+          <t>10,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 22,66</t>
+          <t>10,58; 23,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,87; 27,57</t>
+          <t>15,69; 27,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 15,21</t>
+          <t>3,83; 14,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 44,16</t>
+          <t>6,37; 15,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 61,39</t>
+          <t>24,56; 64,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,37; 61,99</t>
+          <t>30,89; 61,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 31,23</t>
+          <t>7,09; 30,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 230,46</t>
+          <t>11,84; 32,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>5,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,17</t>
+          <t>-3,97; 8,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,91</t>
+          <t>2,21; 13,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 20,19</t>
+          <t>8,23; 20,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,08</t>
+          <t>1,24; 10,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 11,88</t>
+          <t>-5,29; 12,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 19,32</t>
+          <t>2,77; 19,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 32,81</t>
+          <t>12,04; 33,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 13,35</t>
+          <t>1,68; 15,23</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,01</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,62; 16,96</t>
+          <t>5,29; 17,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 8,26</t>
+          <t>-1,15; 7,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,6</t>
+          <t>2,69; 12,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 21,25</t>
+          <t>2,76; 11,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,89; 22,62</t>
+          <t>6,51; 23,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 9,68</t>
+          <t>-1,28; 9,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 15,55</t>
+          <t>3,15; 15,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,5; 29,02</t>
+          <t>3,54; 15,76</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,36</t>
+          <t>5,3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,6</t>
+          <t>-1,04; 8,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 7,75</t>
+          <t>-0,16; 7,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 8,8</t>
+          <t>-0,24; 7,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,78</t>
+          <t>1,53; 9,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 11,33</t>
+          <t>-1,13; 10,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 8,59</t>
+          <t>-0,14; 7,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 9,93</t>
+          <t>-0,23; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 11,79</t>
+          <t>1,68; 11,38</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,93</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,68; 20,45</t>
+          <t>15,47; 20,37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,03</t>
+          <t>17,44; 22,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,82; 17,31</t>
+          <t>12,6; 17,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,03; 29,34</t>
+          <t>8,73; 13,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,4; 52,31</t>
+          <t>37,26; 52,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,5; 45,08</t>
+          <t>33,54; 44,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,34; 35,68</t>
+          <t>24,46; 35,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,5; 75,12</t>
+          <t>16,25; 26,76</t>
         </is>
       </c>
     </row>
